--- a/Zzs/Assets/Excel/Item.xlsx
+++ b/Zzs/Assets/Excel/Item.xlsx
@@ -708,7 +708,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="357">
   <si>
     <t>id</t>
   </si>
@@ -960,9 +960,6 @@
   </si>
   <si>
     <t>印度</t>
-  </si>
-  <si>
-    <t>严格按照说明服用，半个起步</t>
   </si>
   <si>
     <t>10粒</t>
@@ -2279,6 +2276,147 @@
   </si>
   <si>
     <t>莆田鞋，非正品！！！可在得物找图，具体价格私聊，因为款式太多，无法放在上边（一般情况下，不是特别冷门的款式，比如lv什么的，都会有4-5个档次，每个档次之间的价格相差40左右，参考这个价格区间： 150 190 230 280 330这几个档次，不需要每一双都问我，客户问你们的话，可以先报一个价格，然后从我这问到价格后，给它选合适的档次 下单即可…）支持七天无理由退换货，如果是产品原因我这边包邮费，非产品原因 客户出邮费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>印度其他产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严格按照说明服用，半个起步（注意：该产品为较为敏感的产品，不要太高调）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看款式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严格按照说明服用，半个起步，产品价格看图即可（注意：该产品为较为敏感的产品，不要太高调）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练怪兽乳清</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练怪兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悦刻烟杆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悦刻烟弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一次性电子烟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烟弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烟杆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雾都</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看图选口味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看图选口味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>健乐多分离乳清</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴凡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25.7月到期，蛋白质90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>V盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2代</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米柚烟弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看图选颜色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>油仓增加，口感击喉，市面最高品质产品（单买烟弹不能用，必须配合烟杆。口味先看图下单，库存经常更新，这里不做显示，如果缺货下单后我会联系沟通，收获三天内包售后）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>签收时间起两周内质量问题包售后（单买烟杆不能用，必须配合烟弹。颜色先看图下单，库存经常更新，这里不做显示，如果缺货下单后我会联系沟通，收获三天内包售后）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五代通配弹，原版高质量（单买烟弹不能用，必须配合烟杆。口味先看图下单，库存经常更新，这里不做显示，如果缺货下单后我会联系沟通，收获三天内包售后）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超大容量，升级款产品，清凉十足，口感非常nice（口味先看图下单，库存经常更新，这里不做显示，如果缺货下单后我会联系沟通，收获三天内包售后）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>口感好，非常冰，非常冰，非常冰（口味先看图下单，库存经常更新，这里不做显示，如果缺货下单后我会联系沟通，收获三天内包售后）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京/肌霸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>口味更新不全，私聊口味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抖音爆火，价格比平台低就能卖，随缘出一出吧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on健身包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小羽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2360,7 +2498,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2434,12 +2572,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2462,6 +2612,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2471,7 +2630,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2515,9 +2674,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2587,6 +2743,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2865,7 +3042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2884,2874 +3061,3381 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16">
+        <v>2011</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="16">
+        <v>100</v>
+      </c>
+      <c r="D2" s="16">
+        <v>201</v>
+      </c>
+      <c r="E2" s="16">
+        <v>220</v>
+      </c>
+      <c r="F2" s="16">
+        <v>225</v>
+      </c>
+      <c r="G2" s="16">
+        <v>240</v>
+      </c>
+      <c r="H2" s="16">
+        <v>240</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="16">
+        <v>5</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="M2" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="16">
+        <v>2012</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="16">
+        <v>108</v>
+      </c>
+      <c r="D3" s="16">
+        <v>201</v>
+      </c>
+      <c r="E3" s="16">
+        <v>178</v>
+      </c>
+      <c r="F3" s="16">
+        <v>200</v>
+      </c>
+      <c r="G3" s="16">
+        <v>265</v>
+      </c>
+      <c r="H3" s="16">
+        <v>265</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="16">
+        <v>2013</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="16">
+        <v>102</v>
+      </c>
+      <c r="D4" s="16">
+        <v>201</v>
+      </c>
+      <c r="E4" s="16">
+        <v>135</v>
+      </c>
+      <c r="F4" s="16">
+        <v>150</v>
+      </c>
+      <c r="G4" s="16">
+        <v>199</v>
+      </c>
+      <c r="H4" s="16">
+        <v>199</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16">
+        <v>2014</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="16">
+        <v>101</v>
+      </c>
+      <c r="D5" s="16">
+        <v>201</v>
+      </c>
+      <c r="E5" s="16">
+        <v>265</v>
+      </c>
+      <c r="F5" s="16">
+        <v>275</v>
+      </c>
+      <c r="G5" s="16">
+        <v>319</v>
+      </c>
+      <c r="H5" s="16">
+        <v>319</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
+        <v>2015</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="16">
+        <v>101</v>
+      </c>
+      <c r="D6" s="16">
+        <v>201</v>
+      </c>
+      <c r="E6" s="16">
+        <v>295</v>
+      </c>
+      <c r="F6" s="16">
+        <v>315</v>
+      </c>
+      <c r="G6" s="16">
+        <v>360</v>
+      </c>
+      <c r="H6" s="16">
+        <v>360</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16">
+        <v>2016</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="16">
+        <v>111</v>
+      </c>
+      <c r="D7" s="16">
+        <v>201</v>
+      </c>
+      <c r="E7" s="16">
+        <v>95</v>
+      </c>
+      <c r="F7" s="16">
+        <v>110</v>
+      </c>
+      <c r="G7" s="16">
+        <v>140</v>
+      </c>
+      <c r="H7" s="16">
+        <v>140</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16">
+        <v>2017</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="16">
+        <v>110</v>
+      </c>
+      <c r="D8" s="16">
+        <v>201</v>
+      </c>
+      <c r="E8" s="16">
+        <v>279</v>
+      </c>
+      <c r="F8" s="16">
+        <v>285</v>
+      </c>
+      <c r="G8" s="16">
+        <v>299</v>
+      </c>
+      <c r="H8" s="16">
+        <v>299</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="M8" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16">
+        <v>2018</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="16">
+        <v>114</v>
+      </c>
+      <c r="D9" s="16">
+        <v>201</v>
+      </c>
+      <c r="E9" s="16">
+        <v>205</v>
+      </c>
+      <c r="F9" s="16">
+        <v>215</v>
+      </c>
+      <c r="G9" s="16">
+        <v>245</v>
+      </c>
+      <c r="H9" s="16">
+        <v>245</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="16">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="16">
+        <v>119</v>
+      </c>
+      <c r="D10" s="16">
+        <v>201</v>
+      </c>
+      <c r="E10" s="16">
+        <v>75</v>
+      </c>
+      <c r="F10" s="16">
+        <v>80</v>
+      </c>
+      <c r="G10" s="16">
+        <v>95</v>
+      </c>
+      <c r="H10" s="16">
+        <v>95</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="16">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="16">
+        <v>120</v>
+      </c>
+      <c r="D11" s="16">
+        <v>201</v>
+      </c>
+      <c r="E11" s="16">
+        <v>320</v>
+      </c>
+      <c r="F11" s="16">
+        <v>330</v>
+      </c>
+      <c r="G11" s="16">
+        <v>365</v>
+      </c>
+      <c r="H11" s="16">
+        <v>365</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="16">
+        <v>2021</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="16">
+        <v>121</v>
+      </c>
+      <c r="D12" s="16">
+        <v>201</v>
+      </c>
+      <c r="E12" s="16">
+        <v>225</v>
+      </c>
+      <c r="F12" s="16">
+        <v>235</v>
+      </c>
+      <c r="G12" s="16">
+        <v>260</v>
+      </c>
+      <c r="H12" s="16">
+        <v>260</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="16">
+        <v>2022</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="16">
+        <v>125</v>
+      </c>
+      <c r="D13" s="16">
+        <v>201</v>
+      </c>
+      <c r="E13" s="16">
+        <v>335</v>
+      </c>
+      <c r="F13" s="16">
+        <v>340</v>
+      </c>
+      <c r="G13" s="16">
+        <v>358</v>
+      </c>
+      <c r="H13" s="16">
+        <v>358</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="18">
+        <v>2191</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="18">
+        <v>101</v>
+      </c>
+      <c r="D14" s="18">
+        <v>219</v>
+      </c>
+      <c r="E14" s="18">
+        <v>365</v>
+      </c>
+      <c r="F14" s="18">
+        <v>385</v>
+      </c>
+      <c r="G14" s="18">
+        <v>430</v>
+      </c>
+      <c r="H14" s="18">
+        <v>430</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="18">
+        <v>2192</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="18">
+        <v>112</v>
+      </c>
+      <c r="D15" s="18">
+        <v>219</v>
+      </c>
+      <c r="E15" s="18">
+        <v>400</v>
+      </c>
+      <c r="F15" s="18">
+        <v>410</v>
+      </c>
+      <c r="G15" s="18">
+        <v>440</v>
+      </c>
+      <c r="H15" s="18">
+        <v>440</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="18">
+        <v>2193</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="18">
+        <v>114</v>
+      </c>
+      <c r="D16" s="18">
+        <v>219</v>
+      </c>
+      <c r="E16" s="18">
+        <v>355</v>
+      </c>
+      <c r="F16" s="18">
+        <v>360</v>
+      </c>
+      <c r="G16" s="18">
+        <v>380</v>
+      </c>
+      <c r="H16" s="18">
+        <v>380</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="M16" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18">
+        <v>2194</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="18">
+        <v>110</v>
+      </c>
+      <c r="D17" s="18">
+        <v>219</v>
+      </c>
+      <c r="E17" s="18">
+        <v>323</v>
+      </c>
+      <c r="F17" s="18">
+        <v>335</v>
+      </c>
+      <c r="G17" s="18">
+        <v>365</v>
+      </c>
+      <c r="H17" s="18">
+        <v>365</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="18">
+        <v>2195</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="C18" s="18">
+        <v>113</v>
+      </c>
+      <c r="D18" s="18">
+        <v>219</v>
+      </c>
+      <c r="E18" s="18">
+        <v>290</v>
+      </c>
+      <c r="F18" s="18">
+        <v>300</v>
+      </c>
+      <c r="G18" s="18">
+        <v>330</v>
+      </c>
+      <c r="H18" s="18">
+        <v>330</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="20">
+        <v>2021</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="20">
+        <v>108</v>
+      </c>
+      <c r="D19" s="20">
+        <v>202</v>
+      </c>
+      <c r="E19" s="20">
+        <v>70</v>
+      </c>
+      <c r="F19" s="20">
+        <v>80</v>
+      </c>
+      <c r="G19" s="20">
+        <v>125</v>
+      </c>
+      <c r="H19" s="20">
+        <v>125</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="20">
+        <v>2022</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="20">
+        <v>101</v>
+      </c>
+      <c r="D20" s="20">
+        <v>202</v>
+      </c>
+      <c r="E20" s="20">
+        <v>255</v>
+      </c>
+      <c r="F20" s="20">
+        <v>275</v>
+      </c>
+      <c r="G20" s="20">
+        <v>320</v>
+      </c>
+      <c r="H20" s="20">
+        <v>320</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="20">
+        <v>2023</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="20">
+        <v>112</v>
+      </c>
+      <c r="D21" s="20">
+        <v>202</v>
+      </c>
+      <c r="E21" s="20">
+        <v>190</v>
+      </c>
+      <c r="F21" s="20">
+        <v>200</v>
+      </c>
+      <c r="G21" s="20">
+        <v>280</v>
+      </c>
+      <c r="H21" s="20">
+        <v>280</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="20">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="20">
+        <v>113</v>
+      </c>
+      <c r="D22" s="20">
+        <v>202</v>
+      </c>
+      <c r="E22" s="20">
+        <v>35</v>
+      </c>
+      <c r="F22" s="20">
+        <v>40</v>
+      </c>
+      <c r="G22" s="20">
+        <v>48</v>
+      </c>
+      <c r="H22" s="20">
+        <v>48</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="22">
+        <v>2031</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="22">
+        <v>108</v>
+      </c>
+      <c r="D23" s="22">
+        <v>203</v>
+      </c>
+      <c r="E23" s="22">
+        <v>40</v>
+      </c>
+      <c r="F23" s="22">
+        <v>60</v>
+      </c>
+      <c r="G23" s="22">
+        <v>88</v>
+      </c>
+      <c r="H23" s="22">
+        <v>88</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="M23" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="22">
+        <v>2032</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="22">
+        <v>105</v>
+      </c>
+      <c r="D24" s="22">
+        <v>203</v>
+      </c>
+      <c r="E24" s="22">
+        <v>45</v>
+      </c>
+      <c r="F24" s="22">
+        <v>55</v>
+      </c>
+      <c r="G24" s="22">
+        <v>68</v>
+      </c>
+      <c r="H24" s="22">
+        <v>68</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="22">
+        <v>2033</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="22">
+        <v>103</v>
+      </c>
+      <c r="D25" s="22">
+        <v>203</v>
+      </c>
+      <c r="E25" s="22">
+        <v>108</v>
+      </c>
+      <c r="F25" s="22">
+        <v>120</v>
+      </c>
+      <c r="G25" s="22">
+        <v>135</v>
+      </c>
+      <c r="H25" s="22">
+        <v>135</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M25" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="22">
+        <v>2034</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="22">
+        <v>103</v>
+      </c>
+      <c r="D26" s="22">
+        <v>203</v>
+      </c>
+      <c r="E26" s="22">
+        <v>246</v>
+      </c>
+      <c r="F26" s="22">
+        <v>265</v>
+      </c>
+      <c r="G26" s="22">
+        <v>310</v>
+      </c>
+      <c r="H26" s="22">
+        <v>310</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="M26" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="22">
+        <v>2035</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="22">
+        <v>101</v>
+      </c>
+      <c r="D27" s="22">
+        <v>203</v>
+      </c>
+      <c r="E27" s="22">
+        <v>85</v>
+      </c>
+      <c r="F27" s="22">
+        <v>90</v>
+      </c>
+      <c r="G27" s="22">
+        <v>120</v>
+      </c>
+      <c r="H27" s="22">
+        <v>120</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="22">
+        <v>2036</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="22">
         <v>115</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="D28" s="22">
+        <v>203</v>
+      </c>
+      <c r="E28" s="22">
+        <v>13</v>
+      </c>
+      <c r="F28" s="22">
+        <v>18</v>
+      </c>
+      <c r="G28" s="22">
+        <v>23</v>
+      </c>
+      <c r="H28" s="22">
+        <v>23</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="L28" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="22">
+        <v>2037</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="22">
+        <v>118</v>
+      </c>
+      <c r="D29" s="22">
+        <v>203</v>
+      </c>
+      <c r="E29" s="22">
+        <v>53</v>
+      </c>
+      <c r="F29" s="22">
+        <v>60</v>
+      </c>
+      <c r="G29" s="22">
+        <v>78</v>
+      </c>
+      <c r="H29" s="22">
+        <v>78</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="24">
+        <v>2041</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="24">
+        <v>106</v>
+      </c>
+      <c r="D30" s="24">
+        <v>204</v>
+      </c>
+      <c r="E30" s="24">
+        <v>64</v>
+      </c>
+      <c r="F30" s="24">
+        <v>70</v>
+      </c>
+      <c r="G30" s="24">
+        <v>88</v>
+      </c>
+      <c r="H30" s="24">
+        <v>88</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="25" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="24">
+        <v>2042</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="24">
+        <v>113</v>
+      </c>
+      <c r="D31" s="24">
+        <v>204</v>
+      </c>
+      <c r="E31" s="24">
+        <v>20</v>
+      </c>
+      <c r="F31" s="24">
+        <v>25</v>
+      </c>
+      <c r="G31" s="24">
+        <v>35</v>
+      </c>
+      <c r="H31" s="24">
+        <v>35</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="L31" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="M31" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="20">
+        <v>2051</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C32" s="20">
+        <v>117</v>
+      </c>
+      <c r="D32" s="20">
+        <v>205</v>
+      </c>
+      <c r="E32" s="20">
+        <v>35</v>
+      </c>
+      <c r="F32" s="20">
+        <v>40</v>
+      </c>
+      <c r="G32" s="20">
+        <v>60</v>
+      </c>
+      <c r="H32" s="20">
+        <v>60</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="20">
+        <v>2052</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" s="20">
+        <v>117</v>
+      </c>
+      <c r="D33" s="20">
+        <v>205</v>
+      </c>
+      <c r="E33" s="20">
+        <v>43</v>
+      </c>
+      <c r="F33" s="20">
+        <v>50</v>
+      </c>
+      <c r="G33" s="20">
+        <v>68</v>
+      </c>
+      <c r="H33" s="20">
+        <v>68</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="20">
+        <v>2053</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="20">
+        <v>117</v>
+      </c>
+      <c r="D34" s="20">
+        <v>205</v>
+      </c>
+      <c r="E34" s="20">
+        <v>60</v>
+      </c>
+      <c r="F34" s="20">
+        <v>70</v>
+      </c>
+      <c r="G34" s="20">
+        <v>99</v>
+      </c>
+      <c r="H34" s="20">
+        <v>99</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="26">
+        <v>2061</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="26">
+        <v>101</v>
+      </c>
+      <c r="D35" s="26">
+        <v>206</v>
+      </c>
+      <c r="E35" s="26">
+        <v>30</v>
+      </c>
+      <c r="F35" s="26">
+        <v>38</v>
+      </c>
+      <c r="G35" s="26">
+        <v>58</v>
+      </c>
+      <c r="H35" s="26">
+        <v>58</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="L35" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="26">
+        <v>2062</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="26">
+        <v>117</v>
+      </c>
+      <c r="D36" s="26">
+        <v>206</v>
+      </c>
+      <c r="E36" s="26">
+        <v>43</v>
+      </c>
+      <c r="F36" s="26">
+        <v>50</v>
+      </c>
+      <c r="G36" s="26">
+        <v>68</v>
+      </c>
+      <c r="H36" s="26">
+        <v>68</v>
+      </c>
+      <c r="I36" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="L36" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="M36" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="26">
+        <v>2063</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="26">
+        <v>117</v>
+      </c>
+      <c r="D37" s="26">
+        <v>206</v>
+      </c>
+      <c r="E37" s="26">
+        <v>60</v>
+      </c>
+      <c r="F37" s="26">
+        <v>70</v>
+      </c>
+      <c r="G37" s="26">
+        <v>95</v>
+      </c>
+      <c r="H37" s="26">
+        <v>95</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="J37" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="L37" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="M37" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="28">
+        <v>2071</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="28">
+        <v>100</v>
+      </c>
+      <c r="D38" s="28">
+        <v>207</v>
+      </c>
+      <c r="E38" s="28">
+        <v>135</v>
+      </c>
+      <c r="F38" s="28">
+        <v>145</v>
+      </c>
+      <c r="G38" s="28">
+        <v>299</v>
+      </c>
+      <c r="H38" s="28">
+        <v>299</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="K38" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="28">
+        <v>2072</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="28">
+        <v>115</v>
+      </c>
+      <c r="D39" s="28">
+        <v>207</v>
+      </c>
+      <c r="E39" s="28">
+        <v>5</v>
+      </c>
+      <c r="F39" s="28">
+        <v>6</v>
+      </c>
+      <c r="G39" s="28">
+        <v>10</v>
+      </c>
+      <c r="H39" s="28">
+        <v>10</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="L39" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="28">
+        <v>2073</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="28">
+        <v>118</v>
+      </c>
+      <c r="D40" s="28">
+        <v>207</v>
+      </c>
+      <c r="E40" s="28">
+        <v>15</v>
+      </c>
+      <c r="F40" s="28">
+        <v>20</v>
+      </c>
+      <c r="G40" s="28">
+        <v>28</v>
+      </c>
+      <c r="H40" s="28">
+        <v>28</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="L40" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="M40" s="28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="28">
+        <v>2074</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="28">
+        <v>113</v>
+      </c>
+      <c r="D41" s="28">
+        <v>207</v>
+      </c>
+      <c r="E41" s="28">
+        <v>73</v>
+      </c>
+      <c r="F41" s="28">
+        <v>90</v>
+      </c>
+      <c r="G41" s="28">
+        <v>148</v>
+      </c>
+      <c r="H41" s="28">
+        <v>148</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="J41" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="L41" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="M41" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="28">
+        <v>2075</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="C42" s="28">
+        <v>113</v>
+      </c>
+      <c r="D42" s="28">
+        <v>207</v>
+      </c>
+      <c r="E42" s="28">
+        <v>65</v>
+      </c>
+      <c r="F42" s="28">
+        <v>75</v>
+      </c>
+      <c r="G42" s="28">
+        <v>95</v>
+      </c>
+      <c r="H42" s="28">
+        <v>95</v>
+      </c>
+      <c r="I42" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="J42" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="K42" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="L42" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="M42" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="18">
+        <v>2151</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="18">
+        <v>106</v>
+      </c>
+      <c r="D43" s="18">
+        <v>215</v>
+      </c>
+      <c r="E43" s="18">
+        <v>15</v>
+      </c>
+      <c r="F43" s="18">
+        <v>20</v>
+      </c>
+      <c r="G43" s="18">
+        <v>28</v>
+      </c>
+      <c r="H43" s="18">
+        <v>28</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="24">
+        <v>2141</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="24">
+        <v>103</v>
+      </c>
+      <c r="D44" s="24">
+        <v>214</v>
+      </c>
+      <c r="E44" s="24">
+        <v>23</v>
+      </c>
+      <c r="F44" s="24">
+        <v>26</v>
+      </c>
+      <c r="G44" s="24">
+        <v>38</v>
+      </c>
+      <c r="H44" s="24">
+        <v>38</v>
+      </c>
+      <c r="I44" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="J44" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="K44" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="L44" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="M44" s="24" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="24">
+        <v>2142</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" s="24">
+        <v>113</v>
+      </c>
+      <c r="D45" s="24">
+        <v>214</v>
+      </c>
+      <c r="E45" s="24">
+        <v>89</v>
+      </c>
+      <c r="F45" s="24">
+        <v>100</v>
+      </c>
+      <c r="G45" s="24">
+        <v>140</v>
+      </c>
+      <c r="H45" s="24">
+        <v>140</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="J45" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="K45" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="L45" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="M45" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="30">
+        <v>2161</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="30">
+        <v>118</v>
+      </c>
+      <c r="D46" s="30">
+        <v>216</v>
+      </c>
+      <c r="E46" s="30">
+        <v>75</v>
+      </c>
+      <c r="F46" s="30">
+        <v>80</v>
+      </c>
+      <c r="G46" s="30">
+        <v>110</v>
+      </c>
+      <c r="H46" s="30">
+        <v>110</v>
+      </c>
+      <c r="I46" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J46" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="K46" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="L46" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="M46" s="30" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="30">
+        <v>2162</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C47" s="30">
+        <v>118</v>
+      </c>
+      <c r="D47" s="30">
+        <v>216</v>
+      </c>
+      <c r="E47" s="30">
+        <v>30</v>
+      </c>
+      <c r="F47" s="30">
+        <v>36</v>
+      </c>
+      <c r="G47" s="30">
+        <v>48</v>
+      </c>
+      <c r="H47" s="30">
+        <v>48</v>
+      </c>
+      <c r="I47" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="J47" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="K47" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="L47" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="M47" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="32">
+        <v>2201</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="32">
+        <v>115</v>
+      </c>
+      <c r="D48" s="32">
+        <v>220</v>
+      </c>
+      <c r="E48" s="32">
+        <v>4</v>
+      </c>
+      <c r="F48" s="32">
+        <v>6</v>
+      </c>
+      <c r="G48" s="32">
+        <v>8</v>
+      </c>
+      <c r="H48" s="32">
+        <v>8</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="K48" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="L48" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="M48" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="34">
+        <v>2081</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="34">
+        <v>104</v>
+      </c>
+      <c r="D49" s="34">
+        <v>208</v>
+      </c>
+      <c r="E49" s="34">
+        <v>35</v>
+      </c>
+      <c r="F49" s="34">
+        <v>40</v>
+      </c>
+      <c r="G49" s="34">
+        <v>48</v>
+      </c>
+      <c r="H49" s="34">
+        <v>48</v>
+      </c>
+      <c r="I49" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="J49" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="K49" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="L49" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="M49" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="34">
+        <v>2082</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="34">
+        <v>104</v>
+      </c>
+      <c r="D50" s="34">
+        <v>208</v>
+      </c>
+      <c r="E50" s="34">
+        <v>45</v>
+      </c>
+      <c r="F50" s="34">
+        <v>55</v>
+      </c>
+      <c r="G50" s="34">
+        <v>75</v>
+      </c>
+      <c r="H50" s="34">
+        <v>75</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="M50" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="34">
+        <v>2083</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="34">
+        <v>107</v>
+      </c>
+      <c r="D51" s="34">
+        <v>208</v>
+      </c>
+      <c r="E51" s="34">
+        <v>23</v>
+      </c>
+      <c r="F51" s="34">
+        <v>30</v>
+      </c>
+      <c r="G51" s="34">
+        <v>60</v>
+      </c>
+      <c r="H51" s="34">
+        <v>60</v>
+      </c>
+      <c r="I51" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="J51" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K51" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="L51" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M51" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="34">
+        <v>2084</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="34">
+        <v>107</v>
+      </c>
+      <c r="D52" s="34">
+        <v>208</v>
+      </c>
+      <c r="E52" s="34">
+        <v>35</v>
+      </c>
+      <c r="F52" s="34">
+        <v>45</v>
+      </c>
+      <c r="G52" s="34">
+        <v>80</v>
+      </c>
+      <c r="H52" s="34">
+        <v>80</v>
+      </c>
+      <c r="I52" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="J52" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K52" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="L52" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="M52" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="34">
+        <v>2085</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="34">
+        <v>107</v>
+      </c>
+      <c r="D53" s="34">
+        <v>208</v>
+      </c>
+      <c r="E53" s="34">
+        <v>65</v>
+      </c>
+      <c r="F53" s="34">
+        <v>75</v>
+      </c>
+      <c r="G53" s="34">
+        <v>99</v>
+      </c>
+      <c r="H53" s="34">
+        <v>99</v>
+      </c>
+      <c r="I53" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="L53" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="34">
+        <v>2086</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="34">
+        <v>107</v>
+      </c>
+      <c r="D54" s="34">
+        <v>208</v>
+      </c>
+      <c r="E54" s="34">
+        <v>45</v>
+      </c>
+      <c r="F54" s="34">
+        <v>55</v>
+      </c>
+      <c r="G54" s="34">
+        <v>75</v>
+      </c>
+      <c r="H54" s="34">
+        <v>75</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J54" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="L54" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="34">
+        <v>2087</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="34">
+        <v>107</v>
+      </c>
+      <c r="D55" s="34">
+        <v>208</v>
+      </c>
+      <c r="E55" s="34">
+        <v>75</v>
+      </c>
+      <c r="F55" s="34">
+        <v>95</v>
+      </c>
+      <c r="G55" s="34">
+        <v>150</v>
+      </c>
+      <c r="H55" s="34">
+        <v>150</v>
+      </c>
+      <c r="I55" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J55" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="L55" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M55" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="20">
+        <v>2181</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="20">
+        <v>115</v>
+      </c>
+      <c r="D56" s="20">
+        <v>218</v>
+      </c>
+      <c r="E56" s="20">
+        <v>20</v>
+      </c>
+      <c r="F56" s="20">
+        <v>25</v>
+      </c>
+      <c r="G56" s="20">
+        <v>35</v>
+      </c>
+      <c r="H56" s="20">
+        <v>35</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="J56" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L56" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="M56" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="20">
+        <v>2182</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="20">
+        <v>122</v>
+      </c>
+      <c r="D57" s="20">
+        <v>218</v>
+      </c>
+      <c r="E57" s="20">
+        <v>18</v>
+      </c>
+      <c r="F57" s="20">
+        <v>23</v>
+      </c>
+      <c r="G57" s="20">
+        <v>35</v>
+      </c>
+      <c r="H57" s="20">
+        <v>35</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="M57" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="20">
+        <v>2183</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C58" s="20">
+        <v>113</v>
+      </c>
+      <c r="D58" s="20">
+        <v>218</v>
+      </c>
+      <c r="E58" s="20">
+        <v>6</v>
+      </c>
+      <c r="F58" s="20">
+        <v>8</v>
+      </c>
+      <c r="G58" s="20">
+        <v>10</v>
+      </c>
+      <c r="H58" s="20">
+        <v>10</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="J58" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="L58" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="20">
+        <v>2184</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="20">
+        <v>113</v>
+      </c>
+      <c r="D59" s="20">
+        <v>218</v>
+      </c>
+      <c r="E59" s="20">
+        <v>6</v>
+      </c>
+      <c r="F59" s="20">
+        <v>8</v>
+      </c>
+      <c r="G59" s="20">
+        <v>10</v>
+      </c>
+      <c r="H59" s="20">
+        <v>10</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="K59" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="L59" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="M59" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="20">
+        <v>2185</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C60" s="20">
+        <v>113</v>
+      </c>
+      <c r="D60" s="20">
+        <v>218</v>
+      </c>
+      <c r="E60" s="20">
+        <v>43</v>
+      </c>
+      <c r="F60" s="20">
+        <v>50</v>
+      </c>
+      <c r="G60" s="20">
+        <v>78</v>
+      </c>
+      <c r="H60" s="20">
+        <v>199</v>
+      </c>
+      <c r="I60" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="J60" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="18">
+        <v>2111</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="18">
+        <v>109</v>
+      </c>
+      <c r="D61" s="18">
+        <v>211</v>
+      </c>
+      <c r="E61" s="18">
+        <v>400</v>
+      </c>
+      <c r="F61" s="18">
+        <v>500</v>
+      </c>
+      <c r="G61" s="18">
+        <v>850</v>
+      </c>
+      <c r="H61" s="18">
+        <v>850</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L61" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="M61" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="18">
+        <v>2112</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="18">
+        <v>109</v>
+      </c>
+      <c r="D62" s="18">
+        <v>211</v>
+      </c>
+      <c r="E62" s="18">
+        <v>600</v>
+      </c>
+      <c r="F62" s="18">
+        <v>800</v>
+      </c>
+      <c r="G62" s="18">
+        <v>1300</v>
+      </c>
+      <c r="H62" s="18">
+        <v>1300</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="M62" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="18">
+        <v>2113</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="18">
+        <v>109</v>
+      </c>
+      <c r="D63" s="18">
+        <v>211</v>
+      </c>
+      <c r="E63" s="18">
+        <v>880</v>
+      </c>
+      <c r="F63" s="18">
+        <v>1100</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1600</v>
+      </c>
+      <c r="H63" s="18">
+        <v>1600</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L63" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="M63" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="18">
+        <v>2114</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="18">
+        <v>109</v>
+      </c>
+      <c r="D64" s="18">
+        <v>211</v>
+      </c>
+      <c r="E64" s="18">
+        <v>1400</v>
+      </c>
+      <c r="F64" s="18">
+        <v>1650</v>
+      </c>
+      <c r="G64" s="18">
+        <v>2400</v>
+      </c>
+      <c r="H64" s="18">
+        <v>2400</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K64" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L64" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="M64" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="18">
+        <v>2115</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="18">
+        <v>109</v>
+      </c>
+      <c r="D65" s="18">
+        <v>211</v>
+      </c>
+      <c r="E65" s="18">
+        <v>950</v>
+      </c>
+      <c r="F65" s="18">
+        <v>1150</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1800</v>
+      </c>
+      <c r="H65" s="18">
+        <v>1800</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K65" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L65" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="M65" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="18">
+        <v>2116</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="18">
+        <v>109</v>
+      </c>
+      <c r="D66" s="18">
+        <v>211</v>
+      </c>
+      <c r="E66" s="18">
+        <v>300</v>
+      </c>
+      <c r="F66" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G66" s="18">
+        <v>1999</v>
+      </c>
+      <c r="H66" s="18">
+        <v>1999</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="M66" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="18">
+        <v>2117</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="18">
+        <v>109</v>
+      </c>
+      <c r="D67" s="18">
+        <v>211</v>
+      </c>
+      <c r="E67" s="19">
+        <v>780</v>
+      </c>
+      <c r="F67" s="19">
+        <v>1100</v>
+      </c>
+      <c r="G67" s="19">
+        <v>1600</v>
+      </c>
+      <c r="H67" s="19">
+        <v>1600</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K67" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L67" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="M67" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="18">
+        <v>2117</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="C68" s="18">
+        <v>109</v>
+      </c>
+      <c r="D68" s="18">
+        <v>211</v>
+      </c>
+      <c r="E68" s="19">
+        <v>1150</v>
+      </c>
+      <c r="F68" s="19">
+        <v>1600</v>
+      </c>
+      <c r="G68" s="19">
+        <v>1999</v>
+      </c>
+      <c r="H68" s="19">
+        <v>1999</v>
+      </c>
+      <c r="I68" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J68" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K68" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L68" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="M68" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="18">
+        <v>2118</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="18">
+        <v>109</v>
+      </c>
+      <c r="D69" s="18">
+        <v>211</v>
+      </c>
+      <c r="E69" s="18">
+        <v>330</v>
+      </c>
+      <c r="F69" s="18">
+        <v>550</v>
+      </c>
+      <c r="G69" s="18">
+        <v>1250</v>
+      </c>
+      <c r="H69" s="18">
+        <v>1250</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J69" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K69" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="L69" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="M69" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="38" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="36">
+        <v>2091</v>
+      </c>
+      <c r="B70" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" s="36">
         <v>116</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17">
-        <v>2011</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="17">
-        <v>100</v>
-      </c>
-      <c r="D2" s="17">
-        <v>201</v>
-      </c>
-      <c r="E2" s="17">
-        <v>220</v>
-      </c>
-      <c r="F2" s="17">
-        <v>225</v>
-      </c>
-      <c r="G2" s="17">
-        <v>240</v>
-      </c>
-      <c r="H2" s="17">
-        <v>240</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="17">
-        <v>5</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="M2" s="17">
+      <c r="D70" s="36">
+        <v>209</v>
+      </c>
+      <c r="E70" s="36">
+        <v>35</v>
+      </c>
+      <c r="F70" s="36">
+        <v>80</v>
+      </c>
+      <c r="G70" s="36">
+        <v>148</v>
+      </c>
+      <c r="H70" s="36">
+        <v>148</v>
+      </c>
+      <c r="I70" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="J70" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="K70" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="L70" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="M70" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="38" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="36">
+        <v>2092</v>
+      </c>
+      <c r="B71" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="C71" s="36">
+        <v>116</v>
+      </c>
+      <c r="D71" s="36">
+        <v>209</v>
+      </c>
+      <c r="E71" s="36">
+        <v>999</v>
+      </c>
+      <c r="F71" s="36">
+        <v>999</v>
+      </c>
+      <c r="G71" s="36">
+        <v>999</v>
+      </c>
+      <c r="H71" s="36">
+        <v>999</v>
+      </c>
+      <c r="I71" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="K71" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="L71" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="M71" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="16">
+        <v>2211</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C72" s="16">
+        <v>123</v>
+      </c>
+      <c r="D72" s="16">
+        <v>221</v>
+      </c>
+      <c r="E72" s="16">
+        <v>70</v>
+      </c>
+      <c r="F72" s="16">
+        <v>80</v>
+      </c>
+      <c r="G72" s="16">
+        <v>99</v>
+      </c>
+      <c r="H72" s="16">
+        <v>99</v>
+      </c>
+      <c r="I72" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="J72" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="L72" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="M72" s="17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="16">
+        <v>2212</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" s="16">
+        <v>123</v>
+      </c>
+      <c r="D73" s="16">
+        <v>221</v>
+      </c>
+      <c r="E73" s="16">
+        <v>120</v>
+      </c>
+      <c r="F73" s="16">
+        <v>140</v>
+      </c>
+      <c r="G73" s="16">
+        <v>188</v>
+      </c>
+      <c r="H73" s="16">
+        <v>188</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="J73" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="L73" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="M73" s="17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="16">
+        <v>2213</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C74" s="16">
+        <v>124</v>
+      </c>
+      <c r="D74" s="16">
+        <v>221</v>
+      </c>
+      <c r="E74" s="16">
+        <v>999</v>
+      </c>
+      <c r="F74" s="16">
+        <v>999</v>
+      </c>
+      <c r="G74" s="16">
+        <v>999</v>
+      </c>
+      <c r="H74" s="16">
+        <v>999</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="M74" s="17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="20">
+        <v>2101</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C75" s="20">
+        <v>126</v>
+      </c>
+      <c r="D75" s="20">
+        <v>210</v>
+      </c>
+      <c r="E75" s="20">
+        <v>55</v>
+      </c>
+      <c r="F75" s="20">
+        <v>63</v>
+      </c>
+      <c r="G75" s="20">
+        <v>80</v>
+      </c>
+      <c r="H75" s="20">
+        <v>80</v>
+      </c>
+      <c r="I75" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K75" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="L75" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="M75" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="17">
-        <v>2012</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="17">
-        <v>108</v>
-      </c>
-      <c r="D3" s="17">
-        <v>201</v>
-      </c>
-      <c r="E3" s="17">
-        <v>178</v>
-      </c>
-      <c r="F3" s="17">
-        <v>200</v>
-      </c>
-      <c r="G3" s="17">
-        <v>265</v>
-      </c>
-      <c r="H3" s="17">
-        <v>265</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="17">
-        <v>2013</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="17">
-        <v>102</v>
-      </c>
-      <c r="D4" s="17">
-        <v>201</v>
-      </c>
-      <c r="E4" s="17">
-        <v>135</v>
-      </c>
-      <c r="F4" s="17">
-        <v>150</v>
-      </c>
-      <c r="G4" s="17">
-        <v>199</v>
-      </c>
-      <c r="H4" s="17">
-        <v>199</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="17">
-        <v>2014</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="17">
-        <v>101</v>
-      </c>
-      <c r="D5" s="17">
-        <v>201</v>
-      </c>
-      <c r="E5" s="17">
-        <v>265</v>
-      </c>
-      <c r="F5" s="17">
-        <v>275</v>
-      </c>
-      <c r="G5" s="17">
-        <v>319</v>
-      </c>
-      <c r="H5" s="17">
-        <v>319</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17">
-        <v>2015</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="17">
-        <v>101</v>
-      </c>
-      <c r="D6" s="17">
-        <v>201</v>
-      </c>
-      <c r="E6" s="17">
-        <v>295</v>
-      </c>
-      <c r="F6" s="17">
-        <v>315</v>
-      </c>
-      <c r="G6" s="17">
-        <v>360</v>
-      </c>
-      <c r="H6" s="17">
-        <v>360</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="17">
-        <v>2016</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    <row r="76" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="20">
+        <v>2104</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C76" s="20">
+        <v>126</v>
+      </c>
+      <c r="D76" s="20">
+        <v>210</v>
+      </c>
+      <c r="E76" s="20">
+        <v>50</v>
+      </c>
+      <c r="F76" s="20">
+        <v>60</v>
+      </c>
+      <c r="G76" s="20">
         <v>78</v>
       </c>
-      <c r="C7" s="17">
-        <v>111</v>
-      </c>
-      <c r="D7" s="17">
-        <v>201</v>
-      </c>
-      <c r="E7" s="17">
-        <v>95</v>
-      </c>
-      <c r="F7" s="17">
-        <v>110</v>
-      </c>
-      <c r="G7" s="17">
-        <v>140</v>
-      </c>
-      <c r="H7" s="17">
-        <v>140</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="17">
-        <v>2017</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="17">
-        <v>110</v>
-      </c>
-      <c r="D8" s="17">
-        <v>201</v>
-      </c>
-      <c r="E8" s="17">
-        <v>279</v>
-      </c>
-      <c r="F8" s="17">
-        <v>285</v>
-      </c>
-      <c r="G8" s="17">
-        <v>299</v>
-      </c>
-      <c r="H8" s="17">
-        <v>299</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="M8" s="17">
+      <c r="H76" s="20">
+        <v>78</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="L76" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="M76" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="17">
-        <v>2018</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="17">
-        <v>114</v>
-      </c>
-      <c r="D9" s="17">
-        <v>201</v>
-      </c>
-      <c r="E9" s="17">
-        <v>205</v>
-      </c>
-      <c r="F9" s="17">
-        <v>215</v>
-      </c>
-      <c r="G9" s="17">
-        <v>245</v>
-      </c>
-      <c r="H9" s="17">
-        <v>245</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="M9" s="17">
+    <row r="77" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="20">
+        <v>2113</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C77" s="20">
+        <v>127</v>
+      </c>
+      <c r="D77" s="20">
+        <v>210</v>
+      </c>
+      <c r="E77" s="20">
+        <v>105</v>
+      </c>
+      <c r="F77" s="20">
+        <v>120</v>
+      </c>
+      <c r="G77" s="20">
+        <v>160</v>
+      </c>
+      <c r="H77" s="20">
+        <v>160</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K77" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="L77" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="M77" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="17">
-        <v>2019</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="17">
-        <v>119</v>
-      </c>
-      <c r="D10" s="17">
-        <v>201</v>
-      </c>
-      <c r="E10" s="17">
-        <v>75</v>
-      </c>
-      <c r="F10" s="17">
-        <v>80</v>
-      </c>
-      <c r="G10" s="17">
-        <v>95</v>
-      </c>
-      <c r="H10" s="17">
-        <v>95</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="17">
-        <v>2020</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="17">
-        <v>120</v>
-      </c>
-      <c r="D11" s="17">
-        <v>201</v>
-      </c>
-      <c r="E11" s="17">
-        <v>320</v>
-      </c>
-      <c r="F11" s="17">
-        <v>330</v>
-      </c>
-      <c r="G11" s="17">
-        <v>365</v>
-      </c>
-      <c r="H11" s="17">
-        <v>365</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17">
-        <v>2021</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="17">
-        <v>121</v>
-      </c>
-      <c r="D12" s="17">
-        <v>201</v>
-      </c>
-      <c r="E12" s="17">
-        <v>225</v>
-      </c>
-      <c r="F12" s="17">
-        <v>235</v>
-      </c>
-      <c r="G12" s="17">
-        <v>260</v>
-      </c>
-      <c r="H12" s="17">
-        <v>260</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="M12" s="17">
+    <row r="78" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="20">
+        <v>2115</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C78" s="20">
+        <v>128</v>
+      </c>
+      <c r="D78" s="20">
+        <v>210</v>
+      </c>
+      <c r="E78" s="20">
+        <v>60</v>
+      </c>
+      <c r="F78" s="20">
+        <v>70</v>
+      </c>
+      <c r="G78" s="20">
+        <v>90</v>
+      </c>
+      <c r="H78" s="20">
+        <v>90</v>
+      </c>
+      <c r="I78" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K78" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="L78" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="M78" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="19">
-        <v>2191</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="19">
-        <v>101</v>
-      </c>
-      <c r="D13" s="19">
-        <v>219</v>
-      </c>
-      <c r="E13" s="19">
-        <v>365</v>
-      </c>
-      <c r="F13" s="19">
-        <v>385</v>
-      </c>
-      <c r="G13" s="19">
-        <v>430</v>
-      </c>
-      <c r="H13" s="19">
-        <v>430</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="L13" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="19">
-        <v>2192</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="19">
-        <v>112</v>
-      </c>
-      <c r="D14" s="19">
-        <v>219</v>
-      </c>
-      <c r="E14" s="19">
-        <v>400</v>
-      </c>
-      <c r="F14" s="19">
-        <v>410</v>
-      </c>
-      <c r="G14" s="19">
-        <v>440</v>
-      </c>
-      <c r="H14" s="19">
-        <v>440</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="19">
-        <v>2193</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="19">
-        <v>114</v>
-      </c>
-      <c r="D15" s="19">
-        <v>219</v>
-      </c>
-      <c r="E15" s="19">
-        <v>355</v>
-      </c>
-      <c r="F15" s="19">
-        <v>360</v>
-      </c>
-      <c r="G15" s="19">
-        <v>380</v>
-      </c>
-      <c r="H15" s="19">
-        <v>380</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="M15" s="19">
+    <row r="79" spans="1:13" s="8" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="20">
+        <v>2116</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C79" s="20">
+        <v>128</v>
+      </c>
+      <c r="D79" s="20">
+        <v>210</v>
+      </c>
+      <c r="E79" s="20">
+        <v>60</v>
+      </c>
+      <c r="F79" s="20">
+        <v>70</v>
+      </c>
+      <c r="G79" s="20">
+        <v>90</v>
+      </c>
+      <c r="H79" s="20">
+        <v>90</v>
+      </c>
+      <c r="I79" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="L79" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="M79" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="19">
-        <v>2194</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="19">
-        <v>110</v>
-      </c>
-      <c r="D16" s="19">
-        <v>219</v>
-      </c>
-      <c r="E16" s="19">
-        <v>323</v>
-      </c>
-      <c r="F16" s="19">
-        <v>335</v>
-      </c>
-      <c r="G16" s="19">
-        <v>365</v>
-      </c>
-      <c r="H16" s="19">
-        <v>365</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="L16" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="M16" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="21">
-        <v>2021</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="21">
-        <v>108</v>
-      </c>
-      <c r="D17" s="21">
-        <v>202</v>
-      </c>
-      <c r="E17" s="21">
-        <v>70</v>
-      </c>
-      <c r="F17" s="21">
-        <v>80</v>
-      </c>
-      <c r="G17" s="21">
-        <v>125</v>
-      </c>
-      <c r="H17" s="21">
-        <v>125</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="21">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="21">
-        <v>101</v>
-      </c>
-      <c r="D18" s="21">
-        <v>202</v>
-      </c>
-      <c r="E18" s="21">
-        <v>255</v>
-      </c>
-      <c r="F18" s="21">
-        <v>275</v>
-      </c>
-      <c r="G18" s="21">
-        <v>320</v>
-      </c>
-      <c r="H18" s="21">
-        <v>320</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="21">
-        <v>2023</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="21">
-        <v>112</v>
-      </c>
-      <c r="D19" s="21">
-        <v>202</v>
-      </c>
-      <c r="E19" s="21">
-        <v>190</v>
-      </c>
-      <c r="F19" s="21">
-        <v>200</v>
-      </c>
-      <c r="G19" s="21">
-        <v>280</v>
-      </c>
-      <c r="H19" s="21">
-        <v>280</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="L19" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="M19" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="21">
-        <v>2024</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="21">
-        <v>113</v>
-      </c>
-      <c r="D20" s="21">
-        <v>202</v>
-      </c>
-      <c r="E20" s="21">
-        <v>35</v>
-      </c>
-      <c r="F20" s="21">
-        <v>40</v>
-      </c>
-      <c r="G20" s="21">
-        <v>48</v>
-      </c>
-      <c r="H20" s="21">
-        <v>48</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="L20" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="M20" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="23">
-        <v>2031</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="23">
-        <v>108</v>
-      </c>
-      <c r="D21" s="23">
-        <v>203</v>
-      </c>
-      <c r="E21" s="23">
-        <v>40</v>
-      </c>
-      <c r="F21" s="23">
-        <v>60</v>
-      </c>
-      <c r="G21" s="23">
-        <v>88</v>
-      </c>
-      <c r="H21" s="23">
-        <v>88</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="M21" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="23">
-        <v>2032</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="23">
-        <v>105</v>
-      </c>
-      <c r="D22" s="23">
-        <v>203</v>
-      </c>
-      <c r="E22" s="23">
-        <v>45</v>
-      </c>
-      <c r="F22" s="23">
-        <v>55</v>
-      </c>
-      <c r="G22" s="23">
-        <v>68</v>
-      </c>
-      <c r="H22" s="23">
-        <v>68</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="23">
-        <v>2033</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="23">
-        <v>103</v>
-      </c>
-      <c r="D23" s="23">
-        <v>203</v>
-      </c>
-      <c r="E23" s="23">
-        <v>108</v>
-      </c>
-      <c r="F23" s="23">
-        <v>120</v>
-      </c>
-      <c r="G23" s="23">
-        <v>135</v>
-      </c>
-      <c r="H23" s="23">
-        <v>135</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="M23" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="23">
-        <v>2034</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="23">
-        <v>103</v>
-      </c>
-      <c r="D24" s="23">
-        <v>203</v>
-      </c>
-      <c r="E24" s="23">
-        <v>246</v>
-      </c>
-      <c r="F24" s="23">
-        <v>265</v>
-      </c>
-      <c r="G24" s="23">
-        <v>310</v>
-      </c>
-      <c r="H24" s="23">
-        <v>310</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="K24" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="L24" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="M24" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="23">
-        <v>2035</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="23">
-        <v>101</v>
-      </c>
-      <c r="D25" s="23">
-        <v>203</v>
-      </c>
-      <c r="E25" s="23">
-        <v>85</v>
-      </c>
-      <c r="F25" s="23">
-        <v>90</v>
-      </c>
-      <c r="G25" s="23">
-        <v>120</v>
-      </c>
-      <c r="H25" s="23">
-        <v>120</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="23">
-        <v>2036</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="23">
-        <v>115</v>
-      </c>
-      <c r="D26" s="23">
-        <v>203</v>
-      </c>
-      <c r="E26" s="23">
-        <v>13</v>
-      </c>
-      <c r="F26" s="23">
-        <v>18</v>
-      </c>
-      <c r="G26" s="23">
-        <v>23</v>
-      </c>
-      <c r="H26" s="23">
-        <v>23</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="K26" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="L26" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="23">
-        <v>2037</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" s="23">
-        <v>118</v>
-      </c>
-      <c r="D27" s="23">
-        <v>203</v>
-      </c>
-      <c r="E27" s="23">
-        <v>53</v>
-      </c>
-      <c r="F27" s="23">
-        <v>60</v>
-      </c>
-      <c r="G27" s="23">
-        <v>78</v>
-      </c>
-      <c r="H27" s="23">
-        <v>78</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="K27" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="25">
-        <v>2041</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="25">
-        <v>106</v>
-      </c>
-      <c r="D28" s="25">
-        <v>204</v>
-      </c>
-      <c r="E28" s="25">
-        <v>64</v>
-      </c>
-      <c r="F28" s="25">
-        <v>70</v>
-      </c>
-      <c r="G28" s="25">
-        <v>88</v>
-      </c>
-      <c r="H28" s="25">
-        <v>88</v>
-      </c>
-      <c r="I28" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J28" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M28" s="26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="25">
-        <v>2042</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C29" s="25">
-        <v>113</v>
-      </c>
-      <c r="D29" s="25">
-        <v>204</v>
-      </c>
-      <c r="E29" s="25">
-        <v>20</v>
-      </c>
-      <c r="F29" s="25">
-        <v>25</v>
-      </c>
-      <c r="G29" s="25">
-        <v>35</v>
-      </c>
-      <c r="H29" s="25">
-        <v>35</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="J29" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="K29" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="L29" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="M29" s="25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="21">
-        <v>2051</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="C30" s="21">
-        <v>117</v>
-      </c>
-      <c r="D30" s="21">
-        <v>205</v>
-      </c>
-      <c r="E30" s="21">
-        <v>35</v>
-      </c>
-      <c r="F30" s="21">
-        <v>40</v>
-      </c>
-      <c r="G30" s="21">
-        <v>60</v>
-      </c>
-      <c r="H30" s="21">
-        <v>60</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="K30" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="L30" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="M30" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="21">
-        <v>2052</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="C31" s="21">
-        <v>117</v>
-      </c>
-      <c r="D31" s="21">
-        <v>205</v>
-      </c>
-      <c r="E31" s="21">
-        <v>43</v>
-      </c>
-      <c r="F31" s="21">
-        <v>50</v>
-      </c>
-      <c r="G31" s="21">
-        <v>68</v>
-      </c>
-      <c r="H31" s="21">
-        <v>68</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="K31" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="L31" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="M31" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="21">
-        <v>2053</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="C32" s="21">
-        <v>117</v>
-      </c>
-      <c r="D32" s="21">
-        <v>205</v>
-      </c>
-      <c r="E32" s="21">
-        <v>60</v>
-      </c>
-      <c r="F32" s="21">
-        <v>70</v>
-      </c>
-      <c r="G32" s="21">
-        <v>99</v>
-      </c>
-      <c r="H32" s="21">
-        <v>99</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="L32" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="M32" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="27">
-        <v>2061</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="27">
-        <v>101</v>
-      </c>
-      <c r="D33" s="27">
-        <v>206</v>
-      </c>
-      <c r="E33" s="27">
-        <v>30</v>
-      </c>
-      <c r="F33" s="27">
-        <v>38</v>
-      </c>
-      <c r="G33" s="27">
-        <v>58</v>
-      </c>
-      <c r="H33" s="27">
-        <v>58</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="J33" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K33" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="L33" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="M33" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="27">
-        <v>2062</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="27">
-        <v>117</v>
-      </c>
-      <c r="D34" s="27">
-        <v>206</v>
-      </c>
-      <c r="E34" s="27">
-        <v>43</v>
-      </c>
-      <c r="F34" s="27">
-        <v>50</v>
-      </c>
-      <c r="G34" s="27">
-        <v>68</v>
-      </c>
-      <c r="H34" s="27">
-        <v>68</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="J34" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="K34" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="L34" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="M34" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="27">
-        <v>2063</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="27">
-        <v>117</v>
-      </c>
-      <c r="D35" s="27">
-        <v>206</v>
-      </c>
-      <c r="E35" s="27">
-        <v>60</v>
-      </c>
-      <c r="F35" s="27">
-        <v>70</v>
-      </c>
-      <c r="G35" s="27">
-        <v>95</v>
-      </c>
-      <c r="H35" s="27">
-        <v>95</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="L35" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="M35" s="27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="29">
-        <v>2071</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="29">
-        <v>100</v>
-      </c>
-      <c r="D36" s="29">
-        <v>207</v>
-      </c>
-      <c r="E36" s="29">
-        <v>135</v>
-      </c>
-      <c r="F36" s="29">
-        <v>145</v>
-      </c>
-      <c r="G36" s="29">
-        <v>299</v>
-      </c>
-      <c r="H36" s="29">
-        <v>299</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="J36" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="K36" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="L36" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="M36" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="29">
-        <v>2072</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="29">
-        <v>115</v>
-      </c>
-      <c r="D37" s="29">
-        <v>207</v>
-      </c>
-      <c r="E37" s="29">
-        <v>5</v>
-      </c>
-      <c r="F37" s="29">
-        <v>6</v>
-      </c>
-      <c r="G37" s="29">
-        <v>10</v>
-      </c>
-      <c r="H37" s="29">
-        <v>10</v>
-      </c>
-      <c r="I37" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="J37" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="K37" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="L37" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="M37" s="29" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="29">
-        <v>2073</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="C38" s="29">
-        <v>118</v>
-      </c>
-      <c r="D38" s="29">
-        <v>207</v>
-      </c>
-      <c r="E38" s="29">
-        <v>15</v>
-      </c>
-      <c r="F38" s="29">
-        <v>20</v>
-      </c>
-      <c r="G38" s="29">
-        <v>28</v>
-      </c>
-      <c r="H38" s="29">
-        <v>28</v>
-      </c>
-      <c r="I38" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="J38" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="K38" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="L38" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="M38" s="29" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="29">
-        <v>2074</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="C39" s="29">
-        <v>113</v>
-      </c>
-      <c r="D39" s="29">
-        <v>207</v>
-      </c>
-      <c r="E39" s="29">
-        <v>73</v>
-      </c>
-      <c r="F39" s="29">
-        <v>90</v>
-      </c>
-      <c r="G39" s="29">
-        <v>148</v>
-      </c>
-      <c r="H39" s="29">
-        <v>148</v>
-      </c>
-      <c r="I39" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="J39" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="K39" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="L39" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="M39" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="29">
-        <v>2075</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" s="29">
-        <v>113</v>
-      </c>
-      <c r="D40" s="29">
-        <v>207</v>
-      </c>
-      <c r="E40" s="29">
-        <v>65</v>
-      </c>
-      <c r="F40" s="29">
-        <v>75</v>
-      </c>
-      <c r="G40" s="29">
-        <v>95</v>
-      </c>
-      <c r="H40" s="29">
-        <v>95</v>
-      </c>
-      <c r="I40" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="J40" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="K40" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="L40" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="M40" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="19">
-        <v>2151</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="19">
-        <v>106</v>
-      </c>
-      <c r="D41" s="19">
-        <v>215</v>
-      </c>
-      <c r="E41" s="19">
-        <v>15</v>
-      </c>
-      <c r="F41" s="19">
-        <v>20</v>
-      </c>
-      <c r="G41" s="19">
-        <v>28</v>
-      </c>
-      <c r="H41" s="19">
-        <v>28</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="K41" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L41" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="M41" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="25">
-        <v>2141</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="C42" s="25">
-        <v>103</v>
-      </c>
-      <c r="D42" s="25">
-        <v>214</v>
-      </c>
-      <c r="E42" s="25">
-        <v>23</v>
-      </c>
-      <c r="F42" s="25">
-        <v>26</v>
-      </c>
-      <c r="G42" s="25">
-        <v>38</v>
-      </c>
-      <c r="H42" s="25">
-        <v>38</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="K42" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="L42" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="M42" s="25" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="25">
-        <v>2142</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="C43" s="25">
-        <v>113</v>
-      </c>
-      <c r="D43" s="25">
-        <v>214</v>
-      </c>
-      <c r="E43" s="25">
-        <v>89</v>
-      </c>
-      <c r="F43" s="25">
-        <v>100</v>
-      </c>
-      <c r="G43" s="25">
-        <v>140</v>
-      </c>
-      <c r="H43" s="25">
-        <v>140</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="J43" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="K43" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="L43" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="M43" s="25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="31">
-        <v>2161</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="C44" s="31">
-        <v>118</v>
-      </c>
-      <c r="D44" s="31">
-        <v>216</v>
-      </c>
-      <c r="E44" s="31">
-        <v>75</v>
-      </c>
-      <c r="F44" s="31">
-        <v>80</v>
-      </c>
-      <c r="G44" s="31">
-        <v>110</v>
-      </c>
-      <c r="H44" s="31">
-        <v>110</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="J44" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="K44" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="L44" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="M44" s="31" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="31">
-        <v>2162</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C45" s="31">
-        <v>118</v>
-      </c>
-      <c r="D45" s="31">
-        <v>216</v>
-      </c>
-      <c r="E45" s="31">
-        <v>30</v>
-      </c>
-      <c r="F45" s="31">
-        <v>36</v>
-      </c>
-      <c r="G45" s="31">
-        <v>48</v>
-      </c>
-      <c r="H45" s="31">
-        <v>48</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="J45" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="K45" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="L45" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="M45" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="33">
-        <v>2201</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="C46" s="33">
-        <v>115</v>
-      </c>
-      <c r="D46" s="33">
-        <v>220</v>
-      </c>
-      <c r="E46" s="33">
-        <v>4</v>
-      </c>
-      <c r="F46" s="33">
-        <v>6</v>
-      </c>
-      <c r="G46" s="33">
-        <v>8</v>
-      </c>
-      <c r="H46" s="33">
-        <v>8</v>
-      </c>
-      <c r="I46" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="J46" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="K46" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="L46" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="M46" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="35">
-        <v>2081</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="C47" s="35">
-        <v>104</v>
-      </c>
-      <c r="D47" s="35">
-        <v>208</v>
-      </c>
-      <c r="E47" s="35">
-        <v>35</v>
-      </c>
-      <c r="F47" s="35">
-        <v>40</v>
-      </c>
-      <c r="G47" s="35">
-        <v>48</v>
-      </c>
-      <c r="H47" s="35">
-        <v>48</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="J47" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="K47" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="L47" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="M47" s="35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="35">
-        <v>2082</v>
-      </c>
-      <c r="B48" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="35">
-        <v>104</v>
-      </c>
-      <c r="D48" s="35">
-        <v>208</v>
-      </c>
-      <c r="E48" s="35">
-        <v>45</v>
-      </c>
-      <c r="F48" s="35">
-        <v>55</v>
-      </c>
-      <c r="G48" s="35">
-        <v>75</v>
-      </c>
-      <c r="H48" s="35">
-        <v>75</v>
-      </c>
-      <c r="I48" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="J48" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K48" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="L48" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="M48" s="35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="35">
-        <v>2083</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="35">
-        <v>107</v>
-      </c>
-      <c r="D49" s="35">
-        <v>208</v>
-      </c>
-      <c r="E49" s="35">
-        <v>23</v>
-      </c>
-      <c r="F49" s="35">
-        <v>30</v>
-      </c>
-      <c r="G49" s="35">
-        <v>60</v>
-      </c>
-      <c r="H49" s="35">
-        <v>60</v>
-      </c>
-      <c r="I49" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="J49" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K49" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="L49" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="M49" s="35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="35">
-        <v>2084</v>
-      </c>
-      <c r="B50" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C50" s="35">
-        <v>107</v>
-      </c>
-      <c r="D50" s="35">
-        <v>208</v>
-      </c>
-      <c r="E50" s="35">
-        <v>35</v>
-      </c>
-      <c r="F50" s="35">
-        <v>45</v>
-      </c>
-      <c r="G50" s="35">
-        <v>80</v>
-      </c>
-      <c r="H50" s="35">
-        <v>80</v>
-      </c>
-      <c r="I50" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="J50" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K50" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="L50" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="M50" s="35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="35">
-        <v>2085</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" s="35">
-        <v>107</v>
-      </c>
-      <c r="D51" s="35">
-        <v>208</v>
-      </c>
-      <c r="E51" s="35">
-        <v>65</v>
-      </c>
-      <c r="F51" s="35">
-        <v>75</v>
-      </c>
-      <c r="G51" s="35">
-        <v>99</v>
-      </c>
-      <c r="H51" s="35">
-        <v>99</v>
-      </c>
-      <c r="I51" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="J51" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K51" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="L51" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="M51" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="35">
-        <v>2086</v>
-      </c>
-      <c r="B52" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C52" s="35">
-        <v>107</v>
-      </c>
-      <c r="D52" s="35">
-        <v>208</v>
-      </c>
-      <c r="E52" s="35">
-        <v>45</v>
-      </c>
-      <c r="F52" s="35">
-        <v>55</v>
-      </c>
-      <c r="G52" s="35">
-        <v>75</v>
-      </c>
-      <c r="H52" s="35">
-        <v>75</v>
-      </c>
-      <c r="I52" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="J52" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K52" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="L52" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="35">
-        <v>2087</v>
-      </c>
-      <c r="B53" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="C53" s="35">
-        <v>107</v>
-      </c>
-      <c r="D53" s="35">
-        <v>208</v>
-      </c>
-      <c r="E53" s="35">
-        <v>75</v>
-      </c>
-      <c r="F53" s="35">
-        <v>95</v>
-      </c>
-      <c r="G53" s="35">
-        <v>150</v>
-      </c>
-      <c r="H53" s="35">
-        <v>150</v>
-      </c>
-      <c r="I53" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="J53" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="L53" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="M53" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="21">
-        <v>2181</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C54" s="21">
-        <v>115</v>
-      </c>
-      <c r="D54" s="21">
-        <v>218</v>
-      </c>
-      <c r="E54" s="21">
-        <v>20</v>
-      </c>
-      <c r="F54" s="21">
-        <v>25</v>
-      </c>
-      <c r="G54" s="21">
-        <v>35</v>
-      </c>
-      <c r="H54" s="21">
-        <v>35</v>
-      </c>
-      <c r="I54" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="J54" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="K54" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="L54" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="M54" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="21">
-        <v>2182</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C55" s="21">
-        <v>122</v>
-      </c>
-      <c r="D55" s="21">
-        <v>218</v>
-      </c>
-      <c r="E55" s="21">
-        <v>18</v>
-      </c>
-      <c r="F55" s="21">
-        <v>23</v>
-      </c>
-      <c r="G55" s="21">
-        <v>35</v>
-      </c>
-      <c r="H55" s="21">
-        <v>35</v>
-      </c>
-      <c r="I55" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="J55" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="K55" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="L55" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="M55" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="21">
-        <v>2183</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="C56" s="21">
-        <v>113</v>
-      </c>
-      <c r="D56" s="21">
-        <v>218</v>
-      </c>
-      <c r="E56" s="21">
-        <v>6</v>
-      </c>
-      <c r="F56" s="21">
-        <v>8</v>
-      </c>
-      <c r="G56" s="21">
-        <v>10</v>
-      </c>
-      <c r="H56" s="21">
-        <v>10</v>
-      </c>
-      <c r="I56" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="J56" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="K56" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="L56" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="M56" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="21">
-        <v>2184</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="C57" s="21">
-        <v>113</v>
-      </c>
-      <c r="D57" s="21">
-        <v>218</v>
-      </c>
-      <c r="E57" s="21">
-        <v>6</v>
-      </c>
-      <c r="F57" s="21">
-        <v>8</v>
-      </c>
-      <c r="G57" s="21">
-        <v>10</v>
-      </c>
-      <c r="H57" s="21">
-        <v>10</v>
-      </c>
-      <c r="I57" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="J57" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K57" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="L57" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="M57" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="19">
-        <v>2111</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="19">
-        <v>109</v>
-      </c>
-      <c r="D58" s="19">
-        <v>211</v>
-      </c>
-      <c r="E58" s="19">
-        <v>400</v>
-      </c>
-      <c r="F58" s="19">
-        <v>500</v>
-      </c>
-      <c r="G58" s="19">
-        <v>850</v>
-      </c>
-      <c r="H58" s="19">
-        <v>850</v>
-      </c>
-      <c r="I58" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="J58" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L58" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M58" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="19">
-        <v>2112</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="19">
-        <v>109</v>
-      </c>
-      <c r="D59" s="19">
-        <v>211</v>
-      </c>
-      <c r="E59" s="19">
-        <v>600</v>
-      </c>
-      <c r="F59" s="19">
-        <v>800</v>
-      </c>
-      <c r="G59" s="19">
-        <v>1300</v>
-      </c>
-      <c r="H59" s="19">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="J59" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M59" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="19">
-        <v>2113</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" s="19">
-        <v>109</v>
-      </c>
-      <c r="D60" s="19">
-        <v>211</v>
-      </c>
-      <c r="E60" s="19">
-        <v>880</v>
-      </c>
-      <c r="F60" s="19">
-        <v>1100</v>
-      </c>
-      <c r="G60" s="19">
-        <v>1600</v>
-      </c>
-      <c r="H60" s="19">
-        <v>1600</v>
-      </c>
-      <c r="I60" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="J60" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K60" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L60" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M60" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="19">
-        <v>2114</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="19">
-        <v>109</v>
-      </c>
-      <c r="D61" s="19">
-        <v>211</v>
-      </c>
-      <c r="E61" s="19">
-        <v>1400</v>
-      </c>
-      <c r="F61" s="19">
-        <v>1650</v>
-      </c>
-      <c r="G61" s="19">
-        <v>2400</v>
-      </c>
-      <c r="H61" s="19">
-        <v>2400</v>
-      </c>
-      <c r="I61" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="J61" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K61" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L61" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M61" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="19">
-        <v>2115</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" s="19">
-        <v>109</v>
-      </c>
-      <c r="D62" s="19">
-        <v>211</v>
-      </c>
-      <c r="E62" s="19">
-        <v>950</v>
-      </c>
-      <c r="F62" s="19">
-        <v>1150</v>
-      </c>
-      <c r="G62" s="19">
-        <v>1800</v>
-      </c>
-      <c r="H62" s="19">
-        <v>1800</v>
-      </c>
-      <c r="I62" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J62" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="M62" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="19">
-        <v>2116</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C63" s="19">
-        <v>109</v>
-      </c>
-      <c r="D63" s="19">
-        <v>211</v>
-      </c>
-      <c r="E63" s="19">
-        <v>300</v>
-      </c>
-      <c r="F63" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G63" s="19">
-        <v>1999</v>
-      </c>
-      <c r="H63" s="19">
-        <v>1999</v>
-      </c>
-      <c r="I63" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J63" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K63" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="M63" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="19">
-        <v>2117</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C64" s="19">
-        <v>109</v>
-      </c>
-      <c r="D64" s="19">
-        <v>211</v>
-      </c>
-      <c r="E64" s="20">
-        <v>780</v>
-      </c>
-      <c r="F64" s="20">
-        <v>1100</v>
-      </c>
-      <c r="G64" s="20">
-        <v>1600</v>
-      </c>
-      <c r="H64" s="20">
-        <v>1600</v>
-      </c>
-      <c r="I64" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J64" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L64" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="M64" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="19">
-        <v>2117</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="C65" s="19">
-        <v>109</v>
-      </c>
-      <c r="D65" s="19">
-        <v>211</v>
-      </c>
-      <c r="E65" s="20">
-        <v>1150</v>
-      </c>
-      <c r="F65" s="20">
-        <v>1600</v>
-      </c>
-      <c r="G65" s="20">
-        <v>1999</v>
-      </c>
-      <c r="H65" s="20">
-        <v>1999</v>
-      </c>
-      <c r="I65" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J65" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K65" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L65" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="M65" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="19">
-        <v>2118</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" s="19">
-        <v>109</v>
-      </c>
-      <c r="D66" s="19">
-        <v>211</v>
-      </c>
-      <c r="E66" s="19">
-        <v>330</v>
-      </c>
-      <c r="F66" s="19">
-        <v>550</v>
-      </c>
-      <c r="G66" s="19">
-        <v>1250</v>
-      </c>
-      <c r="H66" s="19">
-        <v>1250</v>
-      </c>
-      <c r="I66" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J66" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="L66" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="M66" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="37">
-        <v>2091</v>
-      </c>
-      <c r="B67" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" s="37">
-        <v>116</v>
-      </c>
-      <c r="D67" s="37">
-        <v>209</v>
-      </c>
-      <c r="E67" s="37">
-        <v>35</v>
-      </c>
-      <c r="F67" s="37">
-        <v>80</v>
-      </c>
-      <c r="G67" s="37">
-        <v>148</v>
-      </c>
-      <c r="H67" s="37">
-        <v>148</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="J67" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="L67" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="M67" s="37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="17">
-        <v>2211</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="C68" s="17">
-        <v>123</v>
-      </c>
-      <c r="D68" s="17">
-        <v>221</v>
-      </c>
-      <c r="E68" s="17">
-        <v>70</v>
-      </c>
-      <c r="F68" s="17">
-        <v>80</v>
-      </c>
-      <c r="G68" s="17">
-        <v>99</v>
-      </c>
-      <c r="H68" s="17">
-        <v>99</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="J68" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="K68" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="L68" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="M68" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="17">
-        <v>2212</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C69" s="17">
-        <v>123</v>
-      </c>
-      <c r="D69" s="17">
-        <v>221</v>
-      </c>
-      <c r="E69" s="17">
-        <v>120</v>
-      </c>
-      <c r="F69" s="17">
-        <v>140</v>
-      </c>
-      <c r="G69" s="17">
-        <v>188</v>
-      </c>
-      <c r="H69" s="17">
-        <v>188</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="J69" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="K69" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="L69" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="M69" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="17">
-        <v>2213</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="C70" s="17">
-        <v>124</v>
-      </c>
-      <c r="D70" s="17">
-        <v>221</v>
-      </c>
-      <c r="E70" s="17">
-        <v>999</v>
-      </c>
-      <c r="F70" s="17">
-        <v>999</v>
-      </c>
-      <c r="G70" s="17">
-        <v>999</v>
-      </c>
-      <c r="H70" s="17">
-        <v>999</v>
-      </c>
-      <c r="I70" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="K70" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="L70" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="M70" s="18" t="s">
-        <v>296</v>
-      </c>
+    <row r="80" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="41"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="41"/>
+      <c r="K80" s="42"/>
+      <c r="L80" s="42"/>
+      <c r="M80" s="41"/>
+    </row>
+    <row r="81" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="41"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="42"/>
+      <c r="M81" s="41"/>
+    </row>
+    <row r="82" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="41"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="41"/>
+      <c r="K82" s="42"/>
+      <c r="L82" s="42"/>
+      <c r="M82" s="41"/>
+    </row>
+    <row r="83" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="41"/>
+      <c r="B83" s="42"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="42"/>
+      <c r="L83" s="42"/>
+      <c r="M83" s="41"/>
+    </row>
+    <row r="84" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="41"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="41"/>
+      <c r="K84" s="42"/>
+      <c r="L84" s="42"/>
+      <c r="M84" s="41"/>
+    </row>
+    <row r="85" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="41"/>
+      <c r="B85" s="42"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="41"/>
+      <c r="K85" s="42"/>
+      <c r="L85" s="42"/>
+      <c r="M85" s="41"/>
+    </row>
+    <row r="86" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="41"/>
+      <c r="B86" s="42"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="41"/>
+      <c r="K86" s="42"/>
+      <c r="L86" s="42"/>
+      <c r="M86" s="41"/>
+    </row>
+    <row r="87" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="88" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="41"/>
+      <c r="B88" s="42"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="41"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="41"/>
+      <c r="K88" s="42"/>
+      <c r="L88" s="42"/>
+      <c r="M88" s="41"/>
+    </row>
+    <row r="89" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="90" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="91" spans="1:13" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="41"/>
+      <c r="B91" s="42"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="41"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="41"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="41"/>
+      <c r="K91" s="42"/>
+      <c r="L91" s="42"/>
+      <c r="M91" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5763,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -5772,14 +6456,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>126</v>
+      <c r="C1" s="39" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
@@ -5787,7 +6471,7 @@
         <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
@@ -5809,7 +6493,7 @@
         <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -5897,7 +6581,7 @@
         <v>110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -5919,7 +6603,7 @@
         <v>112</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
@@ -5930,7 +6614,7 @@
         <v>113</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -5941,7 +6625,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -5952,7 +6636,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
@@ -5974,7 +6658,7 @@
         <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -5985,7 +6669,7 @@
         <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -5996,7 +6680,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="1">
         <v>2</v>
@@ -6007,7 +6691,7 @@
         <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
@@ -6018,7 +6702,7 @@
         <v>121</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -6029,7 +6713,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
@@ -6040,7 +6724,7 @@
         <v>123</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
@@ -6051,9 +6735,53 @@
         <v>124</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>125</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>126</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>127</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>128</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C30" s="1">
         <v>3</v>
       </c>
     </row>
@@ -6075,14 +6803,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="39" t="s">
         <v>127</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -6090,7 +6818,7 @@
         <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -6101,7 +6829,7 @@
         <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -6112,7 +6840,7 @@
         <v>202</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -6123,7 +6851,7 @@
         <v>203</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -6134,7 +6862,7 @@
         <v>204</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -6145,7 +6873,7 @@
         <v>205</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -6156,7 +6884,7 @@
         <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>
@@ -6167,7 +6895,7 @@
         <v>207</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -6178,7 +6906,7 @@
         <v>208</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -6200,7 +6928,7 @@
         <v>210</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -6222,7 +6950,7 @@
         <v>213</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
@@ -6233,7 +6961,7 @@
         <v>214</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -6244,7 +6972,7 @@
         <v>215</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -6255,7 +6983,7 @@
         <v>216</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -6266,7 +6994,7 @@
         <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C18" s="1">
         <v>8</v>
@@ -6277,7 +7005,7 @@
         <v>218</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="1">
         <v>5</v>
@@ -6288,7 +7016,7 @@
         <v>219</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
@@ -6299,7 +7027,7 @@
         <v>220</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -6310,7 +7038,7 @@
         <v>221</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C22" s="1">
         <v>6</v>
